--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-16T16:13:27+00:00</t>
+    <t>2025-10-17T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T08:34:24+00:00</t>
+    <t>2025-10-17T12:44:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T12:44:05+00:00</t>
+    <t>2025-10-23T17:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-23T17:09:39+00:00</t>
+    <t>2025-10-24T08:03:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-24T08:03:31+00:00</t>
+    <t>2025-10-24T12:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-24T12:29:28+00:00</t>
+    <t>2025-10-24T14:32:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-24T14:32:29+00:00</t>
+    <t>2025-10-28T09:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T09:05:14+00:00</t>
+    <t>2025-10-28T11:49:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T11:49:38+00:00</t>
+    <t>2025-10-28T12:49:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T12:49:02+00:00</t>
+    <t>2025-10-28T15:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T15:57:21+00:00</t>
+    <t>2025-10-29T13:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
+++ b/ig/DM-OCTOBRE-2025/ValueSet-vs-bdpm-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T13:41:50+00:00</t>
+    <t>2025-10-29T14:58:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
